--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58169</v>
+        <v>58171</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>135385214</v>
       </c>
       <c r="B10" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135385220</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135385222</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>135385216</v>
       </c>
       <c r="B56" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>135385213</v>
       </c>
       <c r="B98" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>135385218</v>
       </c>
       <c r="B99" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>135385214</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135385220</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135385222</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>135385216</v>
       </c>
       <c r="B56" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>135385213</v>
       </c>
       <c r="B98" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>135385218</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>135385214</v>
       </c>
       <c r="B10" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135385220</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135385222</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>135385216</v>
       </c>
       <c r="B56" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>135385213</v>
       </c>
       <c r="B98" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>135385218</v>
       </c>
       <c r="B99" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>135385214</v>
       </c>
       <c r="B10" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135385220</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135385222</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>135385216</v>
       </c>
       <c r="B56" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>135385213</v>
       </c>
       <c r="B98" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>135385218</v>
       </c>
       <c r="B99" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>135385214</v>
       </c>
       <c r="B10" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135385220</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135385222</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>135385216</v>
       </c>
       <c r="B56" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>135385213</v>
       </c>
       <c r="B98" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>135385218</v>
       </c>
       <c r="B99" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
